--- a/InputData/io-model/BPCiOaDCSbIC/BAU Perc Cng in Output and Domestic Content Share by ISIC Code.xlsx
+++ b/InputData/io-model/BPCiOaDCSbIC/BAU Perc Cng in Output and Domestic Content Share by ISIC Code.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MinshuDeng\Desktop\SyncFreeZone\EPS\GitHubRepos\US\eps-us\InputData\io-model\BPCiOaDCSbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806BA151-9951-4CA2-A5FC-3121186185A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C71A5D48-14D2-4D3B-A9F0-46F42EBB3889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{C3094BDE-EEBB-4416-BA99-794B5E057799}"/>
+    <workbookView xWindow="-24840" yWindow="735" windowWidth="23550" windowHeight="15735" firstSheet="5" activeTab="7" xr2:uid="{C3094BDE-EEBB-4416-BA99-794B5E057799}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2775" uniqueCount="1132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1133">
   <si>
     <t>Source:</t>
   </si>
@@ -3538,6 +3538,9 @@
   </si>
   <si>
     <t>should be zero</t>
+  </si>
+  <si>
+    <t>Alternative assigned ISIC Code (two EPS map to one line)</t>
   </si>
 </sst>
 </file>
@@ -3906,8 +3909,10 @@
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Body: normal cell" xfId="9" xr:uid="{1E571901-62A3-490E-A9CE-5146011C1E6C}"/>
@@ -13603,15 +13608,16 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
         <v>265</v>
       </c>
       <c r="L1" s="5"/>
     </row>
-    <row r="2" spans="1:12" ht="66" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="66" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>266</v>
       </c>
@@ -13645,11 +13651,14 @@
       <c r="K2" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="48" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="48" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>277</v>
       </c>
@@ -13684,7 +13693,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="38" t="s">
         <v>280</v>
       </c>
@@ -13719,7 +13728,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
         <v>284</v>
       </c>
@@ -13754,7 +13763,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>286</v>
       </c>
@@ -13792,7 +13801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>288</v>
       </c>
@@ -13827,7 +13836,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>290</v>
       </c>
@@ -13862,7 +13871,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
         <v>292</v>
       </c>
@@ -13897,7 +13906,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="38" t="s">
         <v>294</v>
       </c>
@@ -13932,7 +13941,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
         <v>296</v>
       </c>
@@ -13967,7 +13976,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
         <v>298</v>
       </c>
@@ -14002,7 +14011,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
         <v>300</v>
       </c>
@@ -14037,7 +14046,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>302</v>
       </c>
@@ -14072,7 +14081,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>304</v>
       </c>
@@ -14110,7 +14119,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>306</v>
       </c>
@@ -38558,14 +38567,14 @@
       <c r="A52" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D52" s="48">
+      <c r="D52" s="47">
         <v>0.86499999999999999</v>
       </c>
-      <c r="E52" s="47" t="s">
+      <c r="E52" s="46" t="s">
         <v>1130</v>
       </c>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -48515,111 +48524,111 @@
         <v>2</v>
       </c>
       <c r="C147" s="27">
-        <f>$C5*(1+C57)</f>
+        <f t="shared" ref="C147:C188" si="44">$C5*(1+C57)</f>
         <v>197387000000</v>
       </c>
       <c r="D147" s="27">
-        <f t="shared" ref="D147:AC147" si="44">C147*(1+D57)</f>
+        <f t="shared" ref="D147:AC147" si="45">C147*(1+D57)</f>
         <v>199563522742.02039</v>
       </c>
       <c r="E147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>202219866736.1557</v>
       </c>
       <c r="F147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>204869793771.50421</v>
       </c>
       <c r="G147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>207165131540.63318</v>
       </c>
       <c r="H147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>210197059396.24005</v>
       </c>
       <c r="I147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>213008640895.32449</v>
       </c>
       <c r="J147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>215239920440.1452</v>
       </c>
       <c r="K147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>217440680508.43204</v>
       </c>
       <c r="L147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>219533603652.07773</v>
       </c>
       <c r="M147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>222202468353.77557</v>
       </c>
       <c r="N147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>224975905635.77765</v>
       </c>
       <c r="O147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>228287028528.86255</v>
       </c>
       <c r="P147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>230950169729.72781</v>
       </c>
       <c r="Q147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>233233344326.9325</v>
       </c>
       <c r="R147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>235727720647.32083</v>
       </c>
       <c r="S147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>238000789001.50391</v>
       </c>
       <c r="T147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>239698340371.20529</v>
       </c>
       <c r="U147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>241696797177.5683</v>
       </c>
       <c r="V147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>243711620763.89801</v>
       </c>
       <c r="W147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>245931631708.54517</v>
       </c>
       <c r="X147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>248721748614.19745</v>
       </c>
       <c r="Y147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>251602933070.60361</v>
       </c>
       <c r="Z147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>254457041162.6319</v>
       </c>
       <c r="AA147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>257264933377.48151</v>
       </c>
       <c r="AB147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>260186229595.9631</v>
       </c>
       <c r="AC147" s="27">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>263028599455.96512</v>
       </c>
     </row>
@@ -48631,111 +48640,111 @@
         <v>36</v>
       </c>
       <c r="C148" s="27">
-        <f>$C6*(1+C58)</f>
+        <f t="shared" si="44"/>
         <v>19459700000</v>
       </c>
       <c r="D148" s="27">
-        <f t="shared" ref="D148:AC148" si="45">C148*(1+D58)</f>
+        <f t="shared" ref="D148:AC148" si="46">C148*(1+D58)</f>
         <v>21079087468.998844</v>
       </c>
       <c r="E148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21267988058.100288</v>
       </c>
       <c r="F148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21415757100.461464</v>
       </c>
       <c r="G148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21679576968.624695</v>
       </c>
       <c r="H148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21884512721.855099</v>
       </c>
       <c r="I148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22063212030.405933</v>
       </c>
       <c r="J148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21975523466.033531</v>
       </c>
       <c r="K148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22200467831.526226</v>
       </c>
       <c r="L148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22206322633.674641</v>
       </c>
       <c r="M148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22229920335.104771</v>
       </c>
       <c r="N148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22115585253.580524</v>
       </c>
       <c r="O148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21960761858.172451</v>
       </c>
       <c r="P148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21729028415.554688</v>
       </c>
       <c r="Q148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21618906344.578827</v>
       </c>
       <c r="R148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21477402176.838337</v>
       </c>
       <c r="S148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21529862235.789898</v>
       </c>
       <c r="T148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21608283768.242542</v>
       </c>
       <c r="U148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21706836131.152077</v>
       </c>
       <c r="V148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21703070156.241947</v>
       </c>
       <c r="W148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21753235548.172001</v>
       </c>
       <c r="X148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21816737898.497158</v>
       </c>
       <c r="Y148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21981121001.385185</v>
       </c>
       <c r="Z148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22001886976.536034</v>
       </c>
       <c r="AA148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>21990757849.385464</v>
       </c>
       <c r="AB148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22046332641.265652</v>
       </c>
       <c r="AC148" s="27">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>22114940439.975723</v>
       </c>
     </row>
@@ -48747,111 +48756,111 @@
         <v>37</v>
       </c>
       <c r="C149" s="27">
-        <f>$C7*(1+C59)</f>
+        <f t="shared" si="44"/>
         <v>184888000000</v>
       </c>
       <c r="D149" s="27">
-        <f t="shared" ref="D149:AC149" si="46">C149*(1+D59)</f>
+        <f t="shared" ref="D149:AC149" si="47">C149*(1+D59)</f>
         <v>200273916040.23999</v>
       </c>
       <c r="E149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>202068674033.31223</v>
       </c>
       <c r="F149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>203472638262.15814</v>
       </c>
       <c r="G149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>205979209678.21097</v>
       </c>
       <c r="H149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>207926318911.30618</v>
       </c>
       <c r="I149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>209624153809.03568</v>
       </c>
       <c r="J149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>208791018494.01617</v>
       </c>
       <c r="K149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>210928230981.73251</v>
       </c>
       <c r="L149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>210983857875.24146</v>
       </c>
       <c r="M149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>211208061322.46899</v>
       </c>
       <c r="N149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>210121755544.22705</v>
       </c>
       <c r="O149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>208650767403.08368</v>
       </c>
       <c r="P149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>206449051408.55585</v>
       </c>
       <c r="Q149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>205402773744.53302</v>
       </c>
       <c r="R149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>204058332537.05273</v>
       </c>
       <c r="S149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>204556759305.16507</v>
       </c>
       <c r="T149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>205301847887.83102</v>
       </c>
       <c r="U149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>206238200928.91684</v>
       </c>
       <c r="V149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>206202420132.23529</v>
       </c>
       <c r="W149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>206679045105.03363</v>
       </c>
       <c r="X149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>207282385472.40402</v>
       </c>
       <c r="Y149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>208844201077.30859</v>
       </c>
       <c r="Z149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>209041500090.84375</v>
       </c>
       <c r="AA149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>208935761458.6647</v>
       </c>
       <c r="AB149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>209463781526.86432</v>
       </c>
       <c r="AC149" s="27">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>210115629124.099</v>
       </c>
     </row>
@@ -48863,111 +48872,111 @@
         <v>3</v>
       </c>
       <c r="C150" s="27">
-        <f>$C8*(1+C60)</f>
+        <f t="shared" si="44"/>
         <v>39678400000</v>
       </c>
       <c r="D150" s="27">
-        <f t="shared" ref="D150:AC150" si="47">C150*(1+D60)</f>
+        <f t="shared" ref="D150:AC150" si="48">C150*(1+D60)</f>
         <v>42980337015.982971</v>
       </c>
       <c r="E150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>43365506013.172173</v>
       </c>
       <c r="F150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>43666807635.007233</v>
       </c>
       <c r="G150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44204737318.24633</v>
       </c>
       <c r="H150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44622602074.176651</v>
       </c>
       <c r="I150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44986970622.73616</v>
       </c>
       <c r="J150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44808173316.889</v>
       </c>
       <c r="K150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>45266835706.944626</v>
       </c>
       <c r="L150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>45278773670.097481</v>
       </c>
       <c r="M150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>45326889470.260139</v>
       </c>
       <c r="N150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>45093759817.760277</v>
       </c>
       <c r="O150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44778074344.070564</v>
       </c>
       <c r="P150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44305569000.742317</v>
       </c>
       <c r="Q150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44081029692.273605</v>
       </c>
       <c r="R150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>43792502172.873291</v>
       </c>
       <c r="S150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>43899468426.366592</v>
       </c>
       <c r="T150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44059370219.984634</v>
       </c>
       <c r="U150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44260318851.07708</v>
       </c>
       <c r="V150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44252640014.359451</v>
       </c>
       <c r="W150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44354927433.341118</v>
       </c>
       <c r="X150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44484408959.63092</v>
       </c>
       <c r="Y150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44819586712.09536</v>
       </c>
       <c r="Z150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44861928611.940956</v>
       </c>
       <c r="AA150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44839236280.675255</v>
       </c>
       <c r="AB150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>44952553486.08638</v>
       </c>
       <c r="AC150" s="27">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>45092445040.444244</v>
       </c>
     </row>
@@ -48976,111 +48985,111 @@
         <v>4</v>
       </c>
       <c r="C151" s="27">
-        <f>$C9*(1+C61)</f>
+        <f t="shared" si="44"/>
         <v>51848900000</v>
       </c>
       <c r="D151" s="27">
-        <f t="shared" ref="D151:AC151" si="48">C151*(1+D61)</f>
+        <f t="shared" ref="D151:AC151" si="49">C151*(1+D61)</f>
         <v>51624653507.5</v>
       </c>
       <c r="E151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>51401376881.080063</v>
       </c>
       <c r="F151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>51179065926.069389</v>
       </c>
       <c r="G151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>50957716465.93914</v>
       </c>
       <c r="H151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>50737324342.223953</v>
       </c>
       <c r="I151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>50517885414.443832</v>
       </c>
       <c r="J151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>50299395560.02636</v>
       </c>
       <c r="K151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>50081850674.229248</v>
       </c>
       <c r="L151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>49865246670.063202</v>
       </c>
       <c r="M151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>49649579478.215179</v>
       </c>
       <c r="N151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>49434845046.971901</v>
       </c>
       <c r="O151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>49221039342.143745</v>
       </c>
       <c r="P151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>49008158346.988976</v>
       </c>
       <c r="Q151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>48796198062.138245</v>
       </c>
       <c r="R151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>48585154505.519493</v>
       </c>
       <c r="S151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>48375023712.283119</v>
       </c>
       <c r="T151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>48165801734.727493</v>
       </c>
       <c r="U151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>47957484642.224792</v>
       </c>
       <c r="V151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>47750068521.147171</v>
       </c>
       <c r="W151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>47543549474.793205</v>
       </c>
       <c r="X151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>47337923623.31472</v>
       </c>
       <c r="Y151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>47133187103.643883</v>
       </c>
       <c r="Z151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>46929336069.420624</v>
       </c>
       <c r="AA151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>46726366690.92038</v>
       </c>
       <c r="AB151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>46524275154.982147</v>
       </c>
       <c r="AC151" s="27">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>46323057664.936852</v>
       </c>
     </row>
@@ -49092,111 +49101,111 @@
         <v>5</v>
       </c>
       <c r="C152" s="27">
-        <f>$C10*(1+C62)</f>
+        <f t="shared" si="44"/>
         <v>263619000000</v>
       </c>
       <c r="D152" s="27">
-        <f t="shared" ref="D152:AC152" si="49">C152*(1+D62)</f>
+        <f t="shared" ref="D152:AC152" si="50">C152*(1+D62)</f>
         <v>264340739344.9631</v>
       </c>
       <c r="E152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>264944037288.43829</v>
       </c>
       <c r="F152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>267030806138.04291</v>
       </c>
       <c r="G152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>268737259991.67618</v>
       </c>
       <c r="H152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>270846649316.29962</v>
       </c>
       <c r="I152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>272979209353.32614</v>
       </c>
       <c r="J152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>274931655708.32849</v>
       </c>
       <c r="K152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>276965155504.91705</v>
       </c>
       <c r="L152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>278944488521.55902</v>
       </c>
       <c r="M152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>281024430980.06567</v>
       </c>
       <c r="N152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>282942959071.96838</v>
       </c>
       <c r="O152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>285478137187.95844</v>
       </c>
       <c r="P152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>287803859002.67145</v>
       </c>
       <c r="Q152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>290038782346.12384</v>
       </c>
       <c r="R152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>292405377413.52808</v>
       </c>
       <c r="S152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>294753902750.90295</v>
       </c>
       <c r="T152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>297112105808.95349</v>
       </c>
       <c r="U152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>299516363818.14447</v>
       </c>
       <c r="V152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>301813336481.97174</v>
       </c>
       <c r="W152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>304116901049.85657</v>
       </c>
       <c r="X152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>306358395776.33038</v>
       </c>
       <c r="Y152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>308663083802.54419</v>
       </c>
       <c r="Z152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>311002063027.48889</v>
       </c>
       <c r="AA152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>313354732519.72247</v>
       </c>
       <c r="AB152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>315819901615.81335</v>
       </c>
       <c r="AC152" s="27">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>318229518077.97906</v>
       </c>
     </row>
@@ -49208,111 +49217,111 @@
         <v>6</v>
       </c>
       <c r="C153" s="27">
-        <f>$C11*(1+C63)</f>
+        <f t="shared" si="44"/>
         <v>21056500000</v>
       </c>
       <c r="D153" s="27">
-        <f t="shared" ref="D153:AC153" si="50">C153*(1+D63)</f>
+        <f t="shared" ref="D153:AC153" si="51">C153*(1+D63)</f>
         <v>21199665618.176594</v>
       </c>
       <c r="E153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20995975736.718716</v>
       </c>
       <c r="F153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>21003963543.971237</v>
       </c>
       <c r="G153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20657815352.864571</v>
       </c>
       <c r="H153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20444020517.682438</v>
       </c>
       <c r="I153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20296644820.728176</v>
       </c>
       <c r="J153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>20122611876.069244</v>
       </c>
       <c r="K153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19885602028.01775</v>
       </c>
       <c r="L153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19666998132.061432</v>
       </c>
       <c r="M153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19536937793.918259</v>
       </c>
       <c r="N153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19297474349.933155</v>
       </c>
       <c r="O153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>19062732349.674866</v>
       </c>
       <c r="P153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18967442279.214752</v>
       </c>
       <c r="Q153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18845257598.503475</v>
       </c>
       <c r="R153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18766118695.250576</v>
       </c>
       <c r="S153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18731385386.031128</v>
       </c>
       <c r="T153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18659285795.66711</v>
       </c>
       <c r="U153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18589341266.060783</v>
       </c>
       <c r="V153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18472142473.255638</v>
       </c>
       <c r="W153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18362244251.444241</v>
       </c>
       <c r="X153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18239433825.711067</v>
       </c>
       <c r="Y153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18139347757.382011</v>
       </c>
       <c r="Z153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>18072766129.357204</v>
       </c>
       <c r="AA153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17990117127.883209</v>
       </c>
       <c r="AB153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17917224204.981247</v>
       </c>
       <c r="AC153" s="27">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>17806065572.117599</v>
       </c>
     </row>
@@ -49324,111 +49333,111 @@
         <v>7</v>
       </c>
       <c r="C154" s="27">
-        <f>$C12*(1+C64)</f>
+        <f t="shared" si="44"/>
         <v>44040100000</v>
       </c>
       <c r="D154" s="27">
-        <f t="shared" ref="D154:AC154" si="51">C154*(1+D64)</f>
+        <f t="shared" ref="D154:AC154" si="52">C154*(1+D64)</f>
         <v>44323650285.375694</v>
       </c>
       <c r="E154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>45218682205.361763</v>
       </c>
       <c r="F154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>45758526432.767265</v>
       </c>
       <c r="G154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>46537674588.101952</v>
       </c>
       <c r="H154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>47994641692.084877</v>
       </c>
       <c r="I154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>49122585474.585579</v>
       </c>
       <c r="J154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>49874500110.584473</v>
       </c>
       <c r="K154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50378397864.683975</v>
       </c>
       <c r="L154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50292963119.613701</v>
       </c>
       <c r="M154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50826139155.835464</v>
       </c>
       <c r="N154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>51491178448.950638</v>
       </c>
       <c r="O154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>52955069731.054008</v>
       </c>
       <c r="P154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>53938496804.478165</v>
       </c>
       <c r="Q154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>54283127273.567192</v>
       </c>
       <c r="R154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>54688116956.168411</v>
       </c>
       <c r="S154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>54616244148.388855</v>
       </c>
       <c r="T154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>53552702561.89389</v>
       </c>
       <c r="U154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>52850473558.217125</v>
       </c>
       <c r="V154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>51536647457.290695</v>
       </c>
       <c r="W154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50628084479.556969</v>
       </c>
       <c r="X154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50577356998.303581</v>
       </c>
       <c r="Y154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>50752801583.643547</v>
       </c>
       <c r="Z154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>51303787060.681183</v>
       </c>
       <c r="AA154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>51813110216.238419</v>
       </c>
       <c r="AB154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>52463774858.291763</v>
       </c>
       <c r="AC154" s="27">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>52864971279.921616</v>
       </c>
     </row>
@@ -49440,111 +49449,111 @@
         <v>8</v>
       </c>
       <c r="C155" s="27">
-        <f>$C13*(1+C65)</f>
+        <f t="shared" si="44"/>
         <v>84707600000</v>
       </c>
       <c r="D155" s="27">
-        <f t="shared" ref="D155:AC155" si="52">C155*(1+D65)</f>
+        <f t="shared" ref="D155:AC155" si="53">C155*(1+D65)</f>
         <v>84029584473.284073</v>
       </c>
       <c r="E155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>84067833097.781082</v>
       </c>
       <c r="F155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>82934501769.103897</v>
       </c>
       <c r="G155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>82117915252.276001</v>
       </c>
       <c r="H155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81689058955.781647</v>
       </c>
       <c r="I155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81429518615.632172</v>
       </c>
       <c r="J155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81488791983.091339</v>
       </c>
       <c r="K155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81422626620.942825</v>
       </c>
       <c r="L155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81174751006.607376</v>
       </c>
       <c r="M155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81272535903.244156</v>
       </c>
       <c r="N155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81370328812.940842</v>
       </c>
       <c r="O155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81579057195.344162</v>
       </c>
       <c r="P155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81719285744.139023</v>
       </c>
       <c r="Q155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>81928146914.392609</v>
       </c>
       <c r="R155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>82397079957.771133</v>
       </c>
       <c r="S155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>82892171826.08197</v>
       </c>
       <c r="T155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>83223013899.795822</v>
       </c>
       <c r="U155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>83596888394.785568</v>
       </c>
       <c r="V155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>83890195769.484833</v>
       </c>
       <c r="W155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>84393250711.495834</v>
       </c>
       <c r="X155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>84728672439.747467</v>
       </c>
       <c r="Y155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>85200326107.759735</v>
       </c>
       <c r="Z155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>85633546087.748016</v>
       </c>
       <c r="AA155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>86022767881.951584</v>
       </c>
       <c r="AB155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>86337069092.096161</v>
       </c>
       <c r="AC155" s="27">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>86665996426.06076</v>
       </c>
     </row>
@@ -49556,111 +49565,111 @@
         <v>9</v>
       </c>
       <c r="C156" s="27">
-        <f>$C14*(1+C66)</f>
+        <f t="shared" si="44"/>
         <v>137808000000</v>
       </c>
       <c r="D156" s="27">
-        <f t="shared" ref="D156:AC156" si="53">C156*(1+D66)</f>
+        <f t="shared" ref="D156:AC156" si="54">C156*(1+D66)</f>
         <v>140086898173.53439</v>
       </c>
       <c r="E156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>139475135588.30417</v>
       </c>
       <c r="F156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>138852861923.21628</v>
       </c>
       <c r="G156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>138097946558.2377</v>
       </c>
       <c r="H156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>137020171573.57291</v>
       </c>
       <c r="I156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>135329068792.72488</v>
       </c>
       <c r="J156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>133450421719.57454</v>
       </c>
       <c r="K156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>131228849909.19598</v>
       </c>
       <c r="L156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>128967517039.10101</v>
       </c>
       <c r="M156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>127019902557.81067</v>
       </c>
       <c r="N156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>125068885715.01646</v>
       </c>
       <c r="O156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>123061760271.32571</v>
       </c>
       <c r="P156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>121157993601.48119</v>
       </c>
       <c r="Q156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>119587336733.00711</v>
       </c>
       <c r="R156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>118416474526.67918</v>
       </c>
       <c r="S156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>117556721905.50919</v>
       </c>
       <c r="T156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>116642664887.80774</v>
       </c>
       <c r="U156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>115761194853.35992</v>
       </c>
       <c r="V156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>114967996732.92265</v>
       </c>
       <c r="W156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>114419343011.66115</v>
       </c>
       <c r="X156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113668384216.45651</v>
       </c>
       <c r="Y156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113354742049.09779</v>
       </c>
       <c r="Z156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113536742477.82434</v>
       </c>
       <c r="AA156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113220415463.46054</v>
       </c>
       <c r="AB156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113375829032.65962</v>
       </c>
       <c r="AC156" s="27">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>113554514362.75261</v>
       </c>
     </row>
@@ -49672,111 +49681,111 @@
         <v>33</v>
       </c>
       <c r="C157" s="27">
-        <f>$C15*(1+C67)</f>
+        <f t="shared" si="44"/>
         <v>269741000000</v>
       </c>
       <c r="D157" s="27">
-        <f t="shared" ref="D157:AC157" si="54">C157*(1+D67)</f>
+        <f t="shared" ref="D157:AC157" si="55">C157*(1+D67)</f>
         <v>271134624553.27969</v>
       </c>
       <c r="E157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>269232716368.65161</v>
       </c>
       <c r="F157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>268645660153.63708</v>
       </c>
       <c r="G157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>268117555800.58456</v>
       </c>
       <c r="H157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>269035102558.4133</v>
       </c>
       <c r="I157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>271528039245.88715</v>
       </c>
       <c r="J157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>274759812792.483</v>
       </c>
       <c r="K157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>278402091681.59912</v>
       </c>
       <c r="L157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>281615164903.92407</v>
       </c>
       <c r="M157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>285499281762.5506</v>
       </c>
       <c r="N157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>288936430132.76306</v>
       </c>
       <c r="O157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>291764359311.50983</v>
       </c>
       <c r="P157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>295541225733.6911</v>
       </c>
       <c r="Q157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>299368631525.22186</v>
       </c>
       <c r="R157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>303528401529.86456</v>
       </c>
       <c r="S157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>308196679445.59204</v>
       </c>
       <c r="T157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>312658848956.06525</v>
       </c>
       <c r="U157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>317342954613.18994</v>
       </c>
       <c r="V157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>321448661186.37512</v>
       </c>
       <c r="W157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>325401162004.62781</v>
       </c>
       <c r="X157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>328612218711.82288</v>
       </c>
       <c r="Y157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>332027122336.93024</v>
       </c>
       <c r="Z157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>336690287208.6673</v>
       </c>
       <c r="AA157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>340645537789.93811</v>
       </c>
       <c r="AB157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>344346239214.13849</v>
       </c>
       <c r="AC157" s="27">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>347486875087.85126</v>
       </c>
     </row>
@@ -49785,111 +49794,111 @@
         <v>34</v>
       </c>
       <c r="C158" s="27">
-        <f>$C16*(1+C68)</f>
+        <f t="shared" si="44"/>
         <v>135756000000</v>
       </c>
       <c r="D158" s="27">
-        <f t="shared" ref="D158:AC158" si="55">C158*(1+D68)</f>
+        <f t="shared" ref="D158:AC158" si="56">C158*(1+D68)</f>
         <v>138574294560</v>
       </c>
       <c r="E158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>141451096915.06558</v>
       </c>
       <c r="F158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>144387621687.02234</v>
       </c>
       <c r="G158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>147385108713.2449</v>
       </c>
       <c r="H158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>150444823570.13187</v>
       </c>
       <c r="I158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>153568058107.44778</v>
       </c>
       <c r="J158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>156756130993.75839</v>
       </c>
       <c r="K158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>160010388273.18881</v>
       </c>
       <c r="L158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>163332203933.7402</v>
       </c>
       <c r="M158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>166722980487.40463</v>
       </c>
       <c r="N158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>170184149562.32312</v>
       </c>
       <c r="O158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>173717172507.23694</v>
       </c>
       <c r="P158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>177323541008.48715</v>
       </c>
       <c r="Q158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>181004777719.82333</v>
       </c>
       <c r="R158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>184762436905.28683</v>
       </c>
       <c r="S158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>188598105095.44058</v>
       </c>
       <c r="T158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>192513401757.22189</v>
       </c>
       <c r="U158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>196509979977.70181</v>
       </c>
       <c r="V158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>200589527162.03888</v>
       </c>
       <c r="W158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>204753765745.92279</v>
       </c>
       <c r="X158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>209004453922.80814</v>
       </c>
       <c r="Y158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>213343386386.24561</v>
       </c>
       <c r="Z158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>217772395087.62405</v>
       </c>
       <c r="AA158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>222293350009.6431</v>
       </c>
       <c r="AB158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>226908159955.84326</v>
       </c>
       <c r="AC158" s="27">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>231618773356.52655</v>
       </c>
     </row>
@@ -49901,111 +49910,111 @@
         <v>10</v>
       </c>
       <c r="C159" s="27">
-        <f>$C17*(1+C69)</f>
+        <f t="shared" si="44"/>
         <v>74268200000</v>
       </c>
       <c r="D159" s="27">
-        <f t="shared" ref="D159:AC159" si="56">C159*(1+D69)</f>
+        <f t="shared" ref="D159:AC159" si="57">C159*(1+D69)</f>
         <v>76145452992.428757</v>
       </c>
       <c r="E159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>78600222737.831375</v>
       </c>
       <c r="F159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>80098748335.299545</v>
       </c>
       <c r="G159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>80799127292.256805</v>
       </c>
       <c r="H159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>81823116921.504669</v>
       </c>
       <c r="I159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>83139643935.91925</v>
       </c>
       <c r="J159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>84468451679.207169</v>
       </c>
       <c r="K159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>85730389786.95491</v>
       </c>
       <c r="L159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>86830375476.629364</v>
       </c>
       <c r="M159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>88251314220.309631</v>
       </c>
       <c r="N159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>89335614085.822189</v>
       </c>
       <c r="O159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>90126896320.063141</v>
       </c>
       <c r="P159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>91174898254.556046</v>
       </c>
       <c r="Q159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>92067139203.097183</v>
       </c>
       <c r="R159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>93006272528.594879</v>
       </c>
       <c r="S159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>94070510139.308624</v>
       </c>
       <c r="T159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>94992916699.342041</v>
       </c>
       <c r="U159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>95991656156.654938</v>
       </c>
       <c r="V159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>96687445317.99054</v>
       </c>
       <c r="W159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>97417414150.76004</v>
       </c>
       <c r="X159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>97998261496.167175</v>
       </c>
       <c r="Y159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>98647136594.269104</v>
       </c>
       <c r="Z159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>99405221685.341751</v>
       </c>
       <c r="AA159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>100079992996.57002</v>
       </c>
       <c r="AB159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>100805542725.70563</v>
       </c>
       <c r="AC159" s="27">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>101384265865.28969</v>
       </c>
     </row>
@@ -50017,111 +50026,111 @@
         <v>38</v>
       </c>
       <c r="C160" s="27">
-        <f>$C18*(1+C70)</f>
+        <f t="shared" si="44"/>
         <v>10908300000</v>
       </c>
       <c r="D160" s="27">
-        <f t="shared" ref="D160:AC160" si="57">C160*(1+D70)</f>
+        <f t="shared" ref="D160:AC160" si="58">C160*(1+D70)</f>
         <v>10826587916.398029</v>
       </c>
       <c r="E160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10802554083.151638</v>
       </c>
       <c r="F160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10796320094.709179</v>
       </c>
       <c r="G160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10813234091.73868</v>
       </c>
       <c r="H160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10836664816.224751</v>
       </c>
       <c r="I160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10868066136.587084</v>
       </c>
       <c r="J160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10921400580.002823</v>
       </c>
       <c r="K160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>10990492638.221277</v>
       </c>
       <c r="L160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11058198970.156536</v>
       </c>
       <c r="M160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11132029958.001818</v>
       </c>
       <c r="N160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11215693245.915209</v>
       </c>
       <c r="O160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11297700273.093052</v>
       </c>
       <c r="P160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11389744535.271894</v>
       </c>
       <c r="Q160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11490447934.01964</v>
       </c>
       <c r="R160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11593802773.809803</v>
       </c>
       <c r="S160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11704110145.61606</v>
       </c>
       <c r="T160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11815988854.748953</v>
       </c>
       <c r="U160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11926030268.813519</v>
       </c>
       <c r="V160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12028444340.301331</v>
       </c>
       <c r="W160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12120253156.142881</v>
       </c>
       <c r="X160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12203781176.830095</v>
       </c>
       <c r="Y160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12282365841.480999</v>
       </c>
       <c r="Z160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12367432653.996819</v>
       </c>
       <c r="AA160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12457944735.151342</v>
       </c>
       <c r="AB160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12548876856.639782</v>
       </c>
       <c r="AC160" s="27">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12633557699.889933</v>
       </c>
     </row>
@@ -50133,111 +50142,111 @@
         <v>39</v>
       </c>
       <c r="C161" s="27">
-        <f>$C19*(1+C71)</f>
+        <f t="shared" si="44"/>
         <v>45826900000</v>
       </c>
       <c r="D161" s="27">
-        <f t="shared" ref="D161:AC161" si="58">C161*(1+D71)</f>
+        <f t="shared" ref="D161:AC161" si="59">C161*(1+D71)</f>
         <v>45958693438.928535</v>
       </c>
       <c r="E161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>46080998181.581718</v>
       </c>
       <c r="F161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>46438550364.853828</v>
       </c>
       <c r="G161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>46758198118.475121</v>
       </c>
       <c r="H161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>46892719907.273468</v>
       </c>
       <c r="I161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>47345997802.168526</v>
       </c>
       <c r="J161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>48038845568.180946</v>
       </c>
       <c r="K161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>48636585112.641602</v>
       </c>
       <c r="L161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>49028042790.688263</v>
       </c>
       <c r="M161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>49333804138.680313</v>
       </c>
       <c r="N161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>49744894847.417534</v>
       </c>
       <c r="O161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>50178120082.86689</v>
       </c>
       <c r="P161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>50637175121.278206</v>
       </c>
       <c r="Q161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51157435938.312218</v>
       </c>
       <c r="R161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51625249773.2854</v>
       </c>
       <c r="S161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51899333982.352936</v>
       </c>
       <c r="T161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52036567335.870865</v>
       </c>
       <c r="U161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52074861384.462814</v>
       </c>
       <c r="V161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51889539592.887466</v>
       </c>
       <c r="W161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51550231341.966171</v>
       </c>
       <c r="X161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51568039877.693474</v>
       </c>
       <c r="Y161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>51827634941.64711</v>
       </c>
       <c r="Z161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52139263971.238327</v>
       </c>
       <c r="AA161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52503890332.360764</v>
       </c>
       <c r="AB161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52879528260.659035</v>
       </c>
       <c r="AC161" s="27">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>53289701889.825928</v>
       </c>
     </row>
@@ -50249,111 +50258,111 @@
         <v>40</v>
       </c>
       <c r="C162" s="27">
-        <f>$C20*(1+C72)</f>
+        <f t="shared" si="44"/>
         <v>42096300000</v>
       </c>
       <c r="D162" s="27">
-        <f t="shared" ref="D162:AC162" si="59">C162*(1+D72)</f>
+        <f t="shared" ref="D162:AC162" si="60">C162*(1+D72)</f>
         <v>43174536498.675735</v>
       </c>
       <c r="E162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>44772165738.959099</v>
       </c>
       <c r="F162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>45035326570.967789</v>
       </c>
       <c r="G162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>44751994412.517784</v>
       </c>
       <c r="H162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>44652553924.598846</v>
       </c>
       <c r="I162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>45032608010.418495</v>
       </c>
       <c r="J162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>45617753737.742668</v>
       </c>
       <c r="K162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46178468551.20166</v>
       </c>
       <c r="L162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46037831116.508827</v>
       </c>
       <c r="M162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46353379102.558281</v>
       </c>
       <c r="N162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46637373987.436012</v>
       </c>
       <c r="O162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46874697218.419914</v>
       </c>
       <c r="P162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47491044920.729439</v>
       </c>
       <c r="Q162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47960181029.479645</v>
       </c>
       <c r="R162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48420439804.972374</v>
       </c>
       <c r="S162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>49259632117.868156</v>
       </c>
       <c r="T162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>49803467170.392609</v>
       </c>
       <c r="U162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>50175323623.714714</v>
       </c>
       <c r="V162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>50850631668.969635</v>
       </c>
       <c r="W162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>51377967913.07251</v>
       </c>
       <c r="X162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>51701022676.298393</v>
       </c>
       <c r="Y162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>51899385692.513283</v>
       </c>
       <c r="Z162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>52353398641.222641</v>
       </c>
       <c r="AA162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>52534810119.326775</v>
       </c>
       <c r="AB162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>52620650772.275848</v>
       </c>
       <c r="AC162" s="27">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>52717391128.920464</v>
       </c>
     </row>
@@ -50365,111 +50374,111 @@
         <v>41</v>
       </c>
       <c r="C163" s="27">
-        <f>$C21*(1+C73)</f>
+        <f t="shared" si="44"/>
         <v>19343900000</v>
       </c>
       <c r="D163" s="27">
-        <f t="shared" ref="D163:AC163" si="60">C163*(1+D73)</f>
+        <f t="shared" ref="D163:AC163" si="61">C163*(1+D73)</f>
         <v>19353201620.420277</v>
       </c>
       <c r="E163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>19436462504.019974</v>
       </c>
       <c r="F163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>19678135455.720139</v>
       </c>
       <c r="G163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>19858982767.857227</v>
       </c>
       <c r="H163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>20038169465.769165</v>
       </c>
       <c r="I163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>20219003488.90353</v>
       </c>
       <c r="J163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>20399205943.664795</v>
       </c>
       <c r="K163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>20596912059.477016</v>
       </c>
       <c r="L163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>20798438763.572716</v>
       </c>
       <c r="M163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>21004289675.080807</v>
       </c>
       <c r="N163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>21226181775.852776</v>
       </c>
       <c r="O163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>21448270826.460007</v>
       </c>
       <c r="P163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>21674916982.770981</v>
       </c>
       <c r="Q163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>21906334742.919422</v>
       </c>
       <c r="R163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>22136261749.557041</v>
       </c>
       <c r="S163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>22365467912.982727</v>
       </c>
       <c r="T163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>22592569132.451122</v>
       </c>
       <c r="U163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>22814131734.104237</v>
       </c>
       <c r="V163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23029113212.715477</v>
       </c>
       <c r="W163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23234730033.329414</v>
       </c>
       <c r="X163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23428047030.062084</v>
       </c>
       <c r="Y163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23607619790.540371</v>
       </c>
       <c r="Z163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23780137623.918087</v>
       </c>
       <c r="AA163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>23942492096.160339</v>
       </c>
       <c r="AB163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>24094431568.07452</v>
       </c>
       <c r="AC163" s="27">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>24234367833.463131</v>
       </c>
     </row>
@@ -50481,111 +50490,111 @@
         <v>11</v>
       </c>
       <c r="C164" s="27">
-        <f>$C22*(1+C74)</f>
+        <f t="shared" si="44"/>
         <v>139456000000</v>
       </c>
       <c r="D164" s="27">
-        <f t="shared" ref="D164:AC164" si="61">C164*(1+D74)</f>
+        <f t="shared" ref="D164:AC164" si="62">C164*(1+D74)</f>
         <v>142208690042.59738</v>
       </c>
       <c r="E164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>147893674140.98709</v>
       </c>
       <c r="F164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>151473366045.08997</v>
       </c>
       <c r="G164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>151778990772.8089</v>
       </c>
       <c r="H164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>152152452236.9834</v>
       </c>
       <c r="I164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>153318891376.04297</v>
       </c>
       <c r="J164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>154687265206.17874</v>
       </c>
       <c r="K164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>156237873985.2323</v>
       </c>
       <c r="L164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>156602709982.43057</v>
       </c>
       <c r="M164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>158291722302.81693</v>
       </c>
       <c r="N164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>159070642960.98615</v>
       </c>
       <c r="O164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>160229047279.52252</v>
       </c>
       <c r="P164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>162047415322.85962</v>
       </c>
       <c r="Q164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>163383087811.55356</v>
       </c>
       <c r="R164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>164773665983.01465</v>
       </c>
       <c r="S164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>166528784597.90637</v>
       </c>
       <c r="T164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>167794748817.00439</v>
       </c>
       <c r="U164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>169073278451.51035</v>
       </c>
       <c r="V164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>169817063253.58359</v>
       </c>
       <c r="W164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>171070335259.63547</v>
       </c>
       <c r="X164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>171610835321.59702</v>
       </c>
       <c r="Y164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>172592436240.95529</v>
       </c>
       <c r="Z164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>173433016515.72757</v>
       </c>
       <c r="AA164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>174082905130.73535</v>
       </c>
       <c r="AB164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>175063718060.40726</v>
       </c>
       <c r="AC164" s="27">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>175083023577.18137</v>
       </c>
     </row>
@@ -50597,111 +50606,111 @@
         <v>12</v>
       </c>
       <c r="C165" s="27">
-        <f>$C23*(1+C75)</f>
+        <f t="shared" si="44"/>
         <v>219416000000</v>
       </c>
       <c r="D165" s="27">
-        <f t="shared" ref="D165:AC165" si="62">C165*(1+D75)</f>
+        <f t="shared" ref="D165:AC165" si="63">C165*(1+D75)</f>
         <v>228267677410.22418</v>
       </c>
       <c r="E165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>232992213186.15143</v>
       </c>
       <c r="F165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>242148316877.41043</v>
       </c>
       <c r="G165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>252119151710.33224</v>
       </c>
       <c r="H165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>260184053153.90872</v>
       </c>
       <c r="I165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>267917806296.65298</v>
       </c>
       <c r="J165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>275268352341.66943</v>
       </c>
       <c r="K165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>283087597597.53796</v>
       </c>
       <c r="L165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>289209785912.30322</v>
       </c>
       <c r="M165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>295949714183.17133</v>
       </c>
       <c r="N165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>303581966634.09839</v>
       </c>
       <c r="O165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>312214040192.84668</v>
       </c>
       <c r="P165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>321073067666.92383</v>
       </c>
       <c r="Q165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>330093888296.90112</v>
       </c>
       <c r="R165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>339861492368.34766</v>
       </c>
       <c r="S165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>350347972576.40662</v>
       </c>
       <c r="T165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>361136550381.76947</v>
       </c>
       <c r="U165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>372324040187.23798</v>
       </c>
       <c r="V165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>383353298177.1073</v>
       </c>
       <c r="W165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>395134757911.96185</v>
       </c>
       <c r="X165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>406777616585.20386</v>
       </c>
       <c r="Y165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>419584310498.04254</v>
       </c>
       <c r="Z165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>432914578280.94788</v>
       </c>
       <c r="AA165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>446447695858.65381</v>
       </c>
       <c r="AB165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>460233302091.83636</v>
       </c>
       <c r="AC165" s="27">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>474138761238.68433</v>
       </c>
     </row>
@@ -50713,111 +50722,111 @@
         <v>13</v>
       </c>
       <c r="C166" s="27">
-        <f>$C24*(1+C76)</f>
+        <f t="shared" si="44"/>
         <v>58678400000</v>
       </c>
       <c r="D166" s="27">
-        <f t="shared" ref="D166:AC166" si="63">C166*(1+D76)</f>
+        <f t="shared" ref="D166:AC166" si="64">C166*(1+D76)</f>
         <v>59036821198.028023</v>
       </c>
       <c r="E166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>58619371316.942093</v>
       </c>
       <c r="F166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>59410990856.48671</v>
       </c>
       <c r="G166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>60670034396.672005</v>
       </c>
       <c r="H166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>61590611732.827034</v>
       </c>
       <c r="I166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>62417258676.762512</v>
       </c>
       <c r="J166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>62924156988.707832</v>
       </c>
       <c r="K166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>63487860530.254181</v>
       </c>
       <c r="L166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>63479008280.984497</v>
       </c>
       <c r="M166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>63588553425.96064</v>
       </c>
       <c r="N166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>63866645857.747131</v>
       </c>
       <c r="O166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>64192812958.871727</v>
       </c>
       <c r="P166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>64588943727.21743</v>
       </c>
       <c r="Q166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>64901906819.941635</v>
       </c>
       <c r="R166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>65299688151.934616</v>
       </c>
       <c r="S166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>65790111875.631126</v>
       </c>
       <c r="T166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>66210236410.976791</v>
       </c>
       <c r="U166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>66613076099.584183</v>
       </c>
       <c r="V166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>66934299522.21183</v>
       </c>
       <c r="W166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>67298940380.585457</v>
       </c>
       <c r="X166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>67556451345.339371</v>
       </c>
       <c r="Y166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>67910638967.798798</v>
       </c>
       <c r="Z166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>68333712583.64167</v>
       </c>
       <c r="AA166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>68611006775.606033</v>
       </c>
       <c r="AB166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>68894994363.720108</v>
       </c>
       <c r="AC166" s="27">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>69088455847.137131</v>
       </c>
     </row>
@@ -50829,111 +50838,111 @@
         <v>14</v>
       </c>
       <c r="C167" s="27">
-        <f>$C25*(1+C77)</f>
+        <f t="shared" si="44"/>
         <v>152693000000</v>
       </c>
       <c r="D167" s="27">
-        <f t="shared" ref="D167:AC167" si="64">C167*(1+D77)</f>
+        <f t="shared" ref="D167:AC167" si="65">C167*(1+D77)</f>
         <v>154465985610.28827</v>
       </c>
       <c r="E167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>157616679022.63474</v>
       </c>
       <c r="F167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>163636983106.43906</v>
       </c>
       <c r="G167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>167102159748.98996</v>
       </c>
       <c r="H167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>170065370901.94296</v>
       </c>
       <c r="I167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>173515489220.28043</v>
       </c>
       <c r="J167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>176118746014.97699</v>
       </c>
       <c r="K167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>178458776498.02164</v>
       </c>
       <c r="L167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>179123534723.36307</v>
       </c>
       <c r="M167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>180834755534.15805</v>
       </c>
       <c r="N167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>182177015890.37827</v>
       </c>
       <c r="O167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>183645463046.21692</v>
       </c>
       <c r="P167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>185114645466.78885</v>
       </c>
       <c r="Q167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>185711571805.73337</v>
       </c>
       <c r="R167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>186165627240.3591</v>
       </c>
       <c r="S167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>186903267365.48508</v>
       </c>
       <c r="T167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>187332116285.43933</v>
       </c>
       <c r="U167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>187776664516.49298</v>
       </c>
       <c r="V167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>188008148399.23117</v>
       </c>
       <c r="W167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>188399484983.53897</v>
       </c>
       <c r="X167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>188513976206.29211</v>
       </c>
       <c r="Y167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>189009139856.63266</v>
       </c>
       <c r="Z167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>189808200974.53687</v>
       </c>
       <c r="AA167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>189934434913.07901</v>
       </c>
       <c r="AB167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>190433194955.86758</v>
       </c>
       <c r="AC167" s="27">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>190573736582.50171</v>
       </c>
     </row>
@@ -50945,111 +50954,111 @@
         <v>15</v>
       </c>
       <c r="C168" s="27">
-        <f>$C26*(1+C78)</f>
+        <f t="shared" si="44"/>
         <v>136030000000</v>
       </c>
       <c r="D168" s="27">
-        <f t="shared" ref="D168:AC168" si="65">C168*(1+D78)</f>
+        <f t="shared" ref="D168:AC168" si="66">C168*(1+D78)</f>
         <v>144617922995.31461</v>
       </c>
       <c r="E168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>154359575487.32773</v>
       </c>
       <c r="F168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>157309849492.78455</v>
       </c>
       <c r="G168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>160611189696.79416</v>
       </c>
       <c r="H168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>163612849050.6496</v>
       </c>
       <c r="I168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>165418942759.1694</v>
       </c>
       <c r="J168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>165580206397.42075</v>
       </c>
       <c r="K168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>166929726149.59756</v>
       </c>
       <c r="L168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>168594230111.84854</v>
       </c>
       <c r="M168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>172348054033.12308</v>
       </c>
       <c r="N168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>174787071341.68832</v>
       </c>
       <c r="O168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>176337669076.4946</v>
       </c>
       <c r="P168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>178167666935.16135</v>
       </c>
       <c r="Q168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>180389074071.25238</v>
       </c>
       <c r="R168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>182781667344.64917</v>
       </c>
       <c r="S168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>185017989252.65897</v>
       </c>
       <c r="T168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>186858749470.08618</v>
       </c>
       <c r="U168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>188840415136.68253</v>
       </c>
       <c r="V168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>190431402580.92032</v>
       </c>
       <c r="W168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>192208117762.49567</v>
       </c>
       <c r="X168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>194196533138.96872</v>
       </c>
       <c r="Y168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>196123003128.85501</v>
       </c>
       <c r="Z168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>198002302357.58121</v>
       </c>
       <c r="AA168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>199857790824.68665</v>
       </c>
       <c r="AB168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>201477332607.08881</v>
       </c>
       <c r="AC168" s="27">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>202497761767.72092</v>
       </c>
     </row>
@@ -51061,111 +51070,111 @@
         <v>16</v>
       </c>
       <c r="C169" s="27">
-        <f>$C27*(1+C79)</f>
+        <f t="shared" si="44"/>
         <v>144429000000</v>
       </c>
       <c r="D169" s="27">
-        <f t="shared" ref="D169:AC169" si="66">C169*(1+D79)</f>
+        <f t="shared" ref="D169:AC169" si="67">C169*(1+D79)</f>
         <v>153547173419.76251</v>
       </c>
       <c r="E169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>163890311902.22198</v>
       </c>
       <c r="F169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>167022746838.14877</v>
       </c>
       <c r="G169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>170527924110.25717</v>
       </c>
       <c r="H169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>173714917117.81424</v>
       </c>
       <c r="I169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>175632525794.04599</v>
       </c>
       <c r="J169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>175803746451.32016</v>
       </c>
       <c r="K169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>177236590590.75369</v>
       </c>
       <c r="L169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>179003867241.22745</v>
       </c>
       <c r="M169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>182989466264.42645</v>
       </c>
       <c r="N169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>185579077606.4743</v>
       </c>
       <c r="O169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>187225415033.80896</v>
       </c>
       <c r="P169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>189168403791.65192</v>
       </c>
       <c r="Q169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>191526968896.8382</v>
       </c>
       <c r="R169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>194067289810.48535</v>
       </c>
       <c r="S169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>196441690581.28549</v>
       </c>
       <c r="T169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>198396106206.09467</v>
       </c>
       <c r="U169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>200500127308.50473</v>
       </c>
       <c r="V169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>202189348256.70602</v>
       </c>
       <c r="W169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>204075764466.06973</v>
       </c>
       <c r="X169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>206186952030.64099</v>
       </c>
       <c r="Y169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>208232369469.21548</v>
       </c>
       <c r="Z169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>210227703647.74741</v>
       </c>
       <c r="AA169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>212197756899.35052</v>
       </c>
       <c r="AB169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>213917295237.1478</v>
       </c>
       <c r="AC169" s="27">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>215000729503.41946</v>
       </c>
     </row>
@@ -51177,111 +51186,111 @@
         <v>17</v>
       </c>
       <c r="C170" s="27">
-        <f>$C28*(1+C80)</f>
+        <f t="shared" si="44"/>
         <v>134673000000</v>
       </c>
       <c r="D170" s="27">
-        <f t="shared" ref="D170:AC170" si="67">C170*(1+D80)</f>
+        <f t="shared" ref="D170:AC170" si="68">C170*(1+D80)</f>
         <v>136598194362.90477</v>
       </c>
       <c r="E170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>140428660042.71725</v>
       </c>
       <c r="F170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>144718621015.12631</v>
       </c>
       <c r="G170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>147380507224.22528</v>
       </c>
       <c r="H170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>149145158887.36664</v>
       </c>
       <c r="I170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>152063331056.14417</v>
       </c>
       <c r="J170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>154234877885.14194</v>
       </c>
       <c r="K170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>156908306345.76129</v>
       </c>
       <c r="L170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>158239217835.74033</v>
       </c>
       <c r="M170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>160093402614.20801</v>
       </c>
       <c r="N170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>161752808394.59207</v>
       </c>
       <c r="O170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>163693242935.98828</v>
       </c>
       <c r="P170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>166228976579.49191</v>
       </c>
       <c r="Q170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>167937983339.42889</v>
       </c>
       <c r="R170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>169601870566.65338</v>
       </c>
       <c r="S170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>171843703430.1257</v>
       </c>
       <c r="T170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>173874438310.54727</v>
       </c>
       <c r="U170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>175779545362.05807</v>
       </c>
       <c r="V170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>177638018640.70944</v>
       </c>
       <c r="W170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>179837206381.97198</v>
       </c>
       <c r="X170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>181330925739.39014</v>
       </c>
       <c r="Y170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>183295149430.23218</v>
       </c>
       <c r="Z170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>185552697016.67584</v>
       </c>
       <c r="AA170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>186837139651.03922</v>
       </c>
       <c r="AB170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>189450022624.11295</v>
       </c>
       <c r="AC170" s="27">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>190102585165.06177</v>
       </c>
     </row>
@@ -51290,111 +51299,111 @@
         <v>42</v>
       </c>
       <c r="C171" s="27">
-        <f>$C29*(1+C81)</f>
+        <f t="shared" si="44"/>
         <v>259989000000</v>
       </c>
       <c r="D171" s="27">
-        <f t="shared" ref="D171:AC171" si="68">C171*(1+D81)</f>
+        <f t="shared" ref="D171:AC171" si="69">C171*(1+D81)</f>
         <v>264486809700.00003</v>
       </c>
       <c r="E171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>269062431507.81006</v>
       </c>
       <c r="F171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>273717211572.8952</v>
       </c>
       <c r="G171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>278452519333.10632</v>
       </c>
       <c r="H171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>283269747917.56909</v>
       </c>
       <c r="I171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>288170314556.54309</v>
       </c>
       <c r="J171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>293155660998.37134</v>
       </c>
       <c r="K171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>298227253933.64319</v>
       </c>
       <c r="L171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>303386585426.69525</v>
       </c>
       <c r="M171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>308635173354.57709</v>
       </c>
       <c r="N171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>313974561853.61133</v>
       </c>
       <c r="O171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>319406321773.67883</v>
       </c>
       <c r="P171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>324932051140.36353</v>
       </c>
       <c r="Q171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>330553375625.09186</v>
       </c>
       <c r="R171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>336271949023.40601</v>
       </c>
       <c r="S171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>342089453741.51099</v>
       </c>
       <c r="T171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>348007601291.23914</v>
       </c>
       <c r="U171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>354028132793.57758</v>
       </c>
       <c r="V171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>360152819490.90649</v>
       </c>
       <c r="W171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>366383463268.09918</v>
       </c>
       <c r="X171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>372721897182.63733</v>
       </c>
       <c r="Y171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>379169986003.89697</v>
       </c>
       <c r="Z171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>385729626761.7644</v>
       </c>
       <c r="AA171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>392402749304.74298</v>
       </c>
       <c r="AB171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>399191316867.71509</v>
       </c>
       <c r="AC171" s="27">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>406097326649.52661</v>
       </c>
     </row>
@@ -51403,111 +51412,111 @@
         <v>43</v>
       </c>
       <c r="C172" s="27">
-        <f>$C30*(1+C82)</f>
+        <f t="shared" si="44"/>
         <v>61106700000</v>
       </c>
       <c r="D172" s="27">
-        <f t="shared" ref="D172:AC172" si="69">C172*(1+D82)</f>
+        <f t="shared" ref="D172:AC172" si="70">C172*(1+D82)</f>
         <v>61476701068.499992</v>
       </c>
       <c r="E172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>61848942493.469757</v>
       </c>
       <c r="F172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>62223437840.267708</v>
       </c>
       <c r="G172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>62600200756.390526</v>
       </c>
       <c r="H172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>62979244971.970467</v>
       </c>
       <c r="I172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>63360584300.275742</v>
       </c>
       <c r="J172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>63744232638.213905</v>
       </c>
       <c r="K172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>64130203966.838287</v>
       </c>
       <c r="L172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>64518512351.857491</v>
       </c>
       <c r="M172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>64909171944.14798</v>
       </c>
       <c r="N172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>65302196980.269791</v>
       </c>
       <c r="O172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>65697601782.985321</v>
       </c>
       <c r="P172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>66095400761.781296</v>
       </c>
       <c r="Q172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>66495608413.393875</v>
       </c>
       <c r="R172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>66898239322.336967</v>
       </c>
       <c r="S172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>67303308161.433716</v>
       </c>
       <c r="T172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>67710829692.351189</v>
       </c>
       <c r="U172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>68120818766.138367</v>
       </c>
       <c r="V172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>68533290323.767326</v>
       </c>
       <c r="W172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>68948259396.677734</v>
       </c>
       <c r="X172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>69365741107.324615</v>
       </c>
       <c r="Y172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>69785750669.729462</v>
       </c>
       <c r="Z172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>70208303390.034668</v>
       </c>
       <c r="AA172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>70633414667.061325</v>
       </c>
       <c r="AB172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>71061099992.870377</v>
       </c>
       <c r="AC172" s="27">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>71491374953.327194</v>
       </c>
     </row>
@@ -51516,111 +51525,111 @@
         <v>44</v>
       </c>
       <c r="C173" s="27">
-        <f>$C31*(1+C83)</f>
+        <f t="shared" si="44"/>
         <v>76304000000</v>
       </c>
       <c r="D173" s="27">
-        <f t="shared" ref="D173:AC173" si="70">C173*(1+D83)</f>
+        <f t="shared" ref="D173:AC173" si="71">C173*(1+D83)</f>
         <v>77287310231.985245</v>
       </c>
       <c r="E173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>78283292132.72084</v>
       </c>
       <c r="F173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>79292108998.777588</v>
       </c>
       <c r="G173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>80313926231.087662</v>
       </c>
       <c r="H173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>81348911362.062927</v>
       </c>
       <c r="I173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>82397234083.062836</v>
       </c>
       <c r="J173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>83459066272.216217</v>
       </c>
       <c r="K173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>84534582022.601578</v>
       </c>
       <c r="L173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>85623957670.790665</v>
       </c>
       <c r="M173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>86727371825.759735</v>
       </c>
       <c r="N173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>87845005398.173477</v>
       </c>
       <c r="O173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>88977041630.046295</v>
       </c>
       <c r="P173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>90123666124.785782</v>
       </c>
       <c r="Q173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>91285066877.623428</v>
       </c>
       <c r="R173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>92461434306.437439</v>
       </c>
       <c r="S173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>93652961282.972763</v>
       </c>
       <c r="T173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>94859843164.46344</v>
       </c>
       <c r="U173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>96082277825.662491</v>
       </c>
       <c r="V173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>97320465691.284515</v>
       </c>
       <c r="W173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>98574609768.866409</v>
       </c>
       <c r="X173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>99844915682.051544</v>
       </c>
       <c r="Y173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>101131591704.30287</v>
       </c>
       <c r="Z173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>102434848793.05045</v>
       </c>
       <c r="AA173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>103754900624.27905</v>
       </c>
       <c r="AB173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>105091963627.56152</v>
       </c>
       <c r="AC173" s="27">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>106446257021.54352</v>
       </c>
     </row>
@@ -51632,111 +51641,111 @@
         <v>18</v>
       </c>
       <c r="C174" s="27">
-        <f>$C32*(1+C84)</f>
+        <f t="shared" si="44"/>
         <v>955445000000</v>
       </c>
       <c r="D174" s="27">
-        <f t="shared" ref="D174:AC174" si="71">C174*(1+D84)</f>
+        <f t="shared" ref="D174:AC174" si="72">C174*(1+D84)</f>
         <v>950312009536.55518</v>
       </c>
       <c r="E174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>957718702071.74646</v>
       </c>
       <c r="F174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>972922263165.9978</v>
       </c>
       <c r="G174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>996549967853.89502</v>
       </c>
       <c r="H174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1023895265957.1239</v>
       </c>
       <c r="I174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1043240756620.963</v>
       </c>
       <c r="J174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1060129194710.2522</v>
       </c>
       <c r="K174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1072463672229.3378</v>
       </c>
       <c r="L174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1076958701882.9346</v>
       </c>
       <c r="M174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1077191188118.8772</v>
       </c>
       <c r="N174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1087222578678.9498</v>
       </c>
       <c r="O174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1101145765857.6689</v>
       </c>
       <c r="P174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1109848293989.9124</v>
       </c>
       <c r="Q174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1119176317299.4253</v>
       </c>
       <c r="R174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1127632435326.8433</v>
       </c>
       <c r="S174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1134144963090.166</v>
       </c>
       <c r="T174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1138803834445.3728</v>
       </c>
       <c r="U174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1146440503909.47</v>
       </c>
       <c r="V174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1151940680794.1533</v>
       </c>
       <c r="W174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1157143854267.7041</v>
       </c>
       <c r="X174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1168511474034.6423</v>
       </c>
       <c r="Y174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1181215323008.4458</v>
       </c>
       <c r="Z174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1195798164831.6855</v>
       </c>
       <c r="AA174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1211185966357.3987</v>
       </c>
       <c r="AB174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1227556977245.437</v>
       </c>
       <c r="AC174" s="27">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>1241886124413.6931</v>
       </c>
     </row>
@@ -51745,111 +51754,111 @@
         <v>19</v>
       </c>
       <c r="C175" s="27">
-        <f>$C33*(1+C85)</f>
+        <f t="shared" si="44"/>
         <v>2695700000000</v>
       </c>
       <c r="D175" s="27">
-        <f t="shared" ref="D175:AC175" si="72">C175*(1+D85)</f>
+        <f t="shared" ref="D175:AC175" si="73">C175*(1+D85)</f>
         <v>2754631247730.2178</v>
       </c>
       <c r="E175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2814850803491.3887</v>
       </c>
       <c r="F175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2876386831248.2437</v>
       </c>
       <c r="G175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>2939268110663.6929</v>
       </c>
       <c r="H175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3003524050558.73</v>
       </c>
       <c r="I175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3069184702666.5845</v>
       </c>
       <c r="J175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3136280775687.5581</v>
       </c>
       <c r="K175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3204843649651.1162</v>
       </c>
       <c r="L175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3274905390591.9497</v>
       </c>
       <c r="M175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3346498765546.8779</v>
       </c>
       <c r="N175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3419657257879.5972</v>
       </c>
       <c r="O175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3494415082940.4497</v>
       </c>
       <c r="P175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3570807204068.5327</v>
       </c>
       <c r="Q175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3648869348943.6333</v>
       </c>
       <c r="R175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3728638026295.6367</v>
       </c>
       <c r="S175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3810150542979.2212</v>
       </c>
       <c r="T175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3893445021421.8267</v>
       </c>
       <c r="U175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>3978560417453.0591</v>
       </c>
       <c r="V175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4065536538523.8623</v>
       </c>
       <c r="W175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4154414062323.9893</v>
       </c>
       <c r="X175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4245234555806.4668</v>
       </c>
       <c r="Y175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4338040494627.9648</v>
       </c>
       <c r="Z175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4432875283014.1494</v>
       </c>
       <c r="AA175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4529783274059.3203</v>
       </c>
       <c r="AB175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4628809790469.8213</v>
       </c>
       <c r="AC175" s="27">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4730001145760.9277</v>
       </c>
     </row>
@@ -51858,111 +51867,111 @@
         <v>20</v>
       </c>
       <c r="C176" s="27">
-        <f>$C34*(1+C86)</f>
+        <f t="shared" si="44"/>
         <v>722622000000</v>
       </c>
       <c r="D176" s="27">
-        <f t="shared" ref="D176:AC176" si="73">C176*(1+D86)</f>
+        <f t="shared" ref="D176:AC176" si="74">C176*(1+D86)</f>
         <v>736373496660.00012</v>
       </c>
       <c r="E176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>750386684301.43994</v>
       </c>
       <c r="F176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>764666542903.69641</v>
       </c>
       <c r="G176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>779218147215.15381</v>
       </c>
       <c r="H176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>794046668556.65833</v>
       </c>
       <c r="I176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>809157376659.29163</v>
       </c>
       <c r="J176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>824555641537.11804</v>
       </c>
       <c r="K176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>840246935395.56946</v>
       </c>
       <c r="L176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>856236834576.14722</v>
       </c>
       <c r="M176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>872531021538.13135</v>
       </c>
       <c r="N176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>889135286878.00208</v>
       </c>
       <c r="O176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>906055531387.29053</v>
       </c>
       <c r="P176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>923297768149.5907</v>
       </c>
       <c r="Q176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>940868124677.47754</v>
       </c>
       <c r="R176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>958772845090.09009</v>
       </c>
       <c r="S176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>977018292332.15454</v>
       </c>
       <c r="T176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>995610950435.2356</v>
       </c>
       <c r="U176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1014557426822.0182</v>
       </c>
       <c r="V176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1033864454654.4413</v>
       </c>
       <c r="W176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1053538895226.5154</v>
       </c>
       <c r="X176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1073587740402.676</v>
       </c>
       <c r="Y176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1094018115102.5391</v>
       </c>
       <c r="Z176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1114837279832.9404</v>
       </c>
       <c r="AA176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1136052633268.1614</v>
       </c>
       <c r="AB176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1157671714879.2546</v>
       </c>
       <c r="AC176" s="27">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1179702207613.407</v>
       </c>
     </row>
@@ -51971,111 +51980,111 @@
         <v>21</v>
       </c>
       <c r="C177" s="27">
-        <f>$C35*(1+C87)</f>
+        <f t="shared" si="44"/>
         <v>702900000000</v>
       </c>
       <c r="D177" s="27">
-        <f t="shared" ref="D177:AC177" si="74">C177*(1+D87)</f>
+        <f t="shared" ref="D177:AC177" si="75">C177*(1+D87)</f>
         <v>716884195500</v>
       </c>
       <c r="E177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>731146606569.47253</v>
       </c>
       <c r="F177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>745692768307.17224</v>
       </c>
       <c r="G177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>760528325932.64343</v>
       </c>
       <c r="H177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>775659036977.07336</v>
       </c>
       <c r="I177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>791090773517.73218</v>
       </c>
       <c r="J177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>806829524456.86743</v>
       </c>
       <c r="K177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>822881397845.93677</v>
       </c>
       <c r="L177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>839252623256.08167</v>
       </c>
       <c r="M177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>855949554195.76135</v>
       </c>
       <c r="N177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>872978670576.48596</v>
       </c>
       <c r="O177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>890346581227.6051</v>
       </c>
       <c r="P177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>908060026461.1283</v>
       </c>
       <c r="Q177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>926125880687.57239</v>
       </c>
       <c r="R177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>944551155083.85168</v>
       </c>
       <c r="S177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>963343000314.24487</v>
       </c>
       <c r="T177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>982508709305.49683</v>
       </c>
       <c r="U177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1002055720077.1296</v>
       </c>
       <c r="V177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1021991618628.0641</v>
       </c>
       <c r="W177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1042324141880.6694</v>
       </c>
       <c r="X177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1063061180683.3854</v>
       </c>
       <c r="Y177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1084210782873.0813</v>
       </c>
       <c r="Z177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1105781156398.3413</v>
       </c>
       <c r="AA177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1127780672504.8862</v>
       </c>
       <c r="AB177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1150217868984.3708</v>
       </c>
       <c r="AC177" s="27">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>1173101453487.8149</v>
       </c>
     </row>
@@ -52084,111 +52093,111 @@
         <v>22</v>
       </c>
       <c r="C178" s="27">
-        <f>$C36*(1+C88)</f>
+        <f t="shared" si="44"/>
         <v>502078000000</v>
       </c>
       <c r="D178" s="27">
-        <f t="shared" ref="D178:AC178" si="75">C178*(1+D88)</f>
+        <f t="shared" ref="D178:AC178" si="76">C178*(1+D88)</f>
         <v>518005026461.24969</v>
       </c>
       <c r="E178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>534437293486.51007</v>
       </c>
       <c r="F178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>551390828425.77917</v>
       </c>
       <c r="G178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>568882167052.10376</v>
       </c>
       <c r="H178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>586928369689.88501</v>
       </c>
       <c r="I178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>605547037854.80945</v>
       </c>
       <c r="J178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>624756331421.63562</v>
       </c>
       <c r="K178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>644574986336.58044</v>
       </c>
       <c r="L178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>665022332891.58264</v>
       </c>
       <c r="M178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>686118314578.26526</v>
       </c>
       <c r="N178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>707883507539.98853</v>
       </c>
       <c r="O178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>730339140640.96423</v>
       </c>
       <c r="P178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>753507116172.0072</v>
       </c>
       <c r="Q178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>777410031213.11938</v>
       </c>
       <c r="R178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>802071199673.7417</v>
       </c>
       <c r="S178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>827514675032.172</v>
       </c>
       <c r="T178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>853765273796.32788</v>
       </c>
       <c r="U178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>880848599708.73633</v>
       </c>
       <c r="V178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>908791068719.35974</v>
       </c>
       <c r="W178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>937619934750.61511</v>
       </c>
       <c r="X178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>967363316279.71667</v>
       </c>
       <c r="Y178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>998050223764.26953</v>
       </c>
       <c r="Z178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1029710587937.8635</v>
       </c>
       <c r="AA178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1062375289003.2665</v>
       </c>
       <c r="AB178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1096076186751.6897</v>
       </c>
       <c r="AC178" s="27">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1130846151637.5039</v>
       </c>
     </row>
@@ -52197,111 +52206,111 @@
         <v>23</v>
       </c>
       <c r="C179" s="27">
-        <f>$C37*(1+C89)</f>
+        <f t="shared" si="44"/>
         <v>276414000000</v>
       </c>
       <c r="D179" s="27">
-        <f t="shared" ref="D179:AC179" si="76">C179*(1+D89)</f>
+        <f t="shared" ref="D179:AC179" si="77">C179*(1+D89)</f>
         <v>282869648970</v>
       </c>
       <c r="E179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>289476069621.69434</v>
       </c>
       <c r="F179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>296236783227.70898</v>
       </c>
       <c r="G179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>303155393299.99213</v>
       </c>
       <c r="H179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>310235587510.51343</v>
       </c>
       <c r="I179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>317481139656.82147</v>
       </c>
       <c r="J179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>324895911673.50653</v>
       </c>
       <c r="K179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>332483855690.6413</v>
       </c>
       <c r="L179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>340249016140.2962</v>
       </c>
       <c r="M179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>348195531912.25281</v>
       </c>
       <c r="N179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>356327638560.06348</v>
       </c>
       <c r="O179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>364649670558.63379</v>
       </c>
       <c r="P179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>373166063614.5307</v>
       </c>
       <c r="Q179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>381881357030.24805</v>
       </c>
       <c r="R179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>390800196123.68951</v>
       </c>
       <c r="S179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>399927334704.15826</v>
       </c>
       <c r="T179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>409267637606.17389</v>
       </c>
       <c r="U179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>418826083282.46606</v>
       </c>
       <c r="V179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>428607766457.52808</v>
       </c>
       <c r="W179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>438617900843.14368</v>
       </c>
       <c r="X179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>448861821917.33533</v>
       </c>
       <c r="Y179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>459344989768.21472</v>
       </c>
       <c r="Z179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>470072992004.2514</v>
       </c>
       <c r="AA179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>481051546732.51068</v>
       </c>
       <c r="AB179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>492286505606.44849</v>
       </c>
       <c r="AC179" s="27">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>503783856944.88708</v>
       </c>
     </row>
@@ -52310,111 +52319,111 @@
         <v>24</v>
       </c>
       <c r="C180" s="27">
-        <f>$C38*(1+C90)</f>
+        <f t="shared" si="44"/>
         <v>769467000000</v>
       </c>
       <c r="D180" s="27">
-        <f t="shared" ref="D180:AC180" si="77">C180*(1+D90)</f>
+        <f t="shared" ref="D180:AC180" si="78">C180*(1+D90)</f>
         <v>794759380290</v>
       </c>
       <c r="E180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>820883121120.13232</v>
       </c>
       <c r="F180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>847865549311.35107</v>
       </c>
       <c r="G180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>875734889917.21509</v>
       </c>
       <c r="H180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>904520295748.79395</v>
       </c>
       <c r="I180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>934251877870.05676</v>
       </c>
       <c r="J180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>964960737095.64551</v>
       </c>
       <c r="K180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>996678996523.97937</v>
       </c>
       <c r="L180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1029439835139.7225</v>
       </c>
       <c r="M180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1063277522520.7651</v>
       </c>
       <c r="N180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1098227454686.0226</v>
       </c>
       <c r="O180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1134326191121.552</v>
       </c>
       <c r="P180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1171611493023.7173</v>
       </c>
       <c r="Q180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1210122362799.4067</v>
       </c>
       <c r="R180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1249899084864.6233</v>
       </c>
       <c r="S180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1290983267784.1233</v>
       </c>
       <c r="T180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1333417887796.1873</v>
       </c>
       <c r="U180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1377247333768.0479</v>
       </c>
       <c r="V180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1422517453629.0034</v>
       </c>
       <c r="W180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1469275602329.7886</v>
       </c>
       <c r="X180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1517570691378.3687</v>
       </c>
       <c r="Y180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1567453240003.9756</v>
       </c>
       <c r="Z180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1618975428002.9063</v>
       </c>
       <c r="AA180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1672191150321.3618</v>
       </c>
       <c r="AB180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1727156073432.4248</v>
       </c>
       <c r="AC180" s="27">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>1783927693566.1484</v>
       </c>
     </row>
@@ -52423,111 +52432,111 @@
         <v>25</v>
       </c>
       <c r="C181" s="27">
-        <f>$C39*(1+C91)</f>
+        <f t="shared" si="44"/>
         <v>1631550000000</v>
       </c>
       <c r="D181" s="27">
-        <f t="shared" ref="D181:AC181" si="78">C181*(1+D91)</f>
+        <f t="shared" ref="D181:AC181" si="79">C181*(1+D91)</f>
         <v>1659775815000.0002</v>
       </c>
       <c r="E181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1688489936599.5005</v>
       </c>
       <c r="F181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1717700812502.6721</v>
       </c>
       <c r="G181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1747417036558.9685</v>
       </c>
       <c r="H181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1777647351291.4387</v>
       </c>
       <c r="I181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1808400650468.7808</v>
       </c>
       <c r="J181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1839685981721.8909</v>
       </c>
       <c r="K181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1871512549205.6797</v>
       </c>
       <c r="L181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1903889716306.9382</v>
       </c>
       <c r="M181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1936827008399.0483</v>
       </c>
       <c r="N181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>1970334115644.3521</v>
       </c>
       <c r="O181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2004420895844.9995</v>
       </c>
       <c r="P181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2039097377343.1182</v>
       </c>
       <c r="Q181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2074373761971.1543</v>
       </c>
       <c r="R181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2110260428053.2554</v>
       </c>
       <c r="S181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2146767933458.5769</v>
       </c>
       <c r="T181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2183907018707.4104</v>
       </c>
       <c r="U181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2221688610131.0488</v>
       </c>
       <c r="V181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2260123823086.3164</v>
       </c>
       <c r="W181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2299223965225.71</v>
       </c>
       <c r="X181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2339000539824.1147</v>
       </c>
       <c r="Y181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2379465249163.0723</v>
       </c>
       <c r="Z181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2420629997973.5938</v>
       </c>
       <c r="AA181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2462506896938.5371</v>
       </c>
       <c r="AB181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2505108266255.5742</v>
       </c>
       <c r="AC181" s="27">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2548446639261.7959</v>
       </c>
     </row>
@@ -52536,111 +52545,111 @@
         <v>26</v>
       </c>
       <c r="C182" s="27">
-        <f>$C40*(1+C92)</f>
+        <f t="shared" si="44"/>
         <v>2966020000000</v>
       </c>
       <c r="D182" s="27">
-        <f t="shared" ref="D182:AC182" si="79">C182*(1+D92)</f>
+        <f t="shared" ref="D182:AC182" si="80">C182*(1+D92)</f>
         <v>3014766538700</v>
       </c>
       <c r="E182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3064314226763.5347</v>
       </c>
       <c r="F182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3114676231080.3931</v>
       </c>
       <c r="G182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3165865934938.1992</v>
       </c>
       <c r="H182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3217896941578.9087</v>
       </c>
       <c r="I182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3270783077813.7578</v>
       </c>
       <c r="J182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3324538397697.627</v>
       </c>
       <c r="K182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3379177186263.7876</v>
       </c>
       <c r="L182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3434713963320.0327</v>
       </c>
       <c r="M182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3491163487307.1973</v>
       </c>
       <c r="N182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3548540759221.0908</v>
       </c>
       <c r="O182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3606861026598.8892</v>
       </c>
       <c r="P182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3666139787571.042</v>
       </c>
       <c r="Q182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3726392794979.772</v>
       </c>
       <c r="R182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3787636060565.2646</v>
       </c>
       <c r="S182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3849885859220.6548</v>
       </c>
       <c r="T182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3913158733316.9463</v>
       </c>
       <c r="U182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3977471497099.0103</v>
       </c>
       <c r="V182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4042841241153.8325</v>
       </c>
       <c r="W182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4109285336952.1958</v>
       </c>
       <c r="X182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4176821441465.0049</v>
       </c>
       <c r="Y182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4245467501855.4819</v>
       </c>
       <c r="Z182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4315241760248.4766</v>
       </c>
       <c r="AA182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4386162758578.1602</v>
       </c>
       <c r="AB182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4458249343515.3926</v>
       </c>
       <c r="AC182" s="27">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>4531520671476.0684</v>
       </c>
     </row>
@@ -52649,111 +52658,111 @@
         <v>27</v>
       </c>
       <c r="C183" s="27">
-        <f>$C41*(1+C93)</f>
+        <f t="shared" si="44"/>
         <v>2342320000000</v>
       </c>
       <c r="D183" s="27">
-        <f t="shared" ref="D183:AC183" si="80">C183*(1+D93)</f>
+        <f t="shared" ref="D183:AC183" si="81">C183*(1+D93)</f>
         <v>2389528913670.2749</v>
       </c>
       <c r="E183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2437689311992.4878</v>
       </c>
       <c r="F183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2486820371918.0342</v>
       </c>
       <c r="G183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2536941656905.2944</v>
       </c>
       <c r="H183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2588073124709.5938</v>
       </c>
       <c r="I183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2640235135330.1641</v>
       </c>
       <c r="J183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2693448459117.2764</v>
       </c>
       <c r="K183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2747734285042.77</v>
       </c>
       <c r="L183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2803114229137.2739</v>
       </c>
       <c r="M183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2859610343097.4761</v>
       </c>
       <c r="N183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2917245123066.8716</v>
       </c>
       <c r="O183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>2976041518593.4839</v>
       </c>
       <c r="P183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3036022941768.1284</v>
       </c>
       <c r="Q183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3097213276546.8545</v>
       </c>
       <c r="R183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3159636888261.2788</v>
       </c>
       <c r="S183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3223318633320.5972</v>
       </c>
       <c r="T183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3288283869109.1406</v>
       </c>
       <c r="U183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3354558464083.4102</v>
       </c>
       <c r="V183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3422168808072.6191</v>
       </c>
       <c r="W183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3491141822786.8374</v>
       </c>
       <c r="X183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3561504972536.9272</v>
       </c>
       <c r="Y183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3633286275170.5342</v>
       </c>
       <c r="Z183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3706514313228.4941</v>
       </c>
       <c r="AA183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3781218245326.0908</v>
       </c>
       <c r="AB183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3857427817763.7031</v>
       </c>
       <c r="AC183" s="27">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3935173376371.4609</v>
       </c>
     </row>
@@ -52762,111 +52771,111 @@
         <v>28</v>
       </c>
       <c r="C184" s="27">
-        <f>$C42*(1+C94)</f>
+        <f t="shared" si="44"/>
         <v>2412650000000</v>
       </c>
       <c r="D184" s="27">
-        <f t="shared" ref="D184:AC184" si="81">C184*(1+D94)</f>
+        <f t="shared" ref="D184:AC184" si="82">C184*(1+D94)</f>
         <v>2423220808178.729</v>
       </c>
       <c r="E184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2433837931399.2383</v>
       </c>
       <c r="F184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2444501572586.7026</v>
       </c>
       <c r="G184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2455211935555.395</v>
       </c>
       <c r="H184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2465969225012.582</v>
       </c>
       <c r="I184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2476773646562.437</v>
       </c>
       <c r="J184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2487625406709.9688</v>
       </c>
       <c r="K184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2498524712864.9702</v>
       </c>
       <c r="L184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2509471773345.9805</v>
       </c>
       <c r="M184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2520466797384.2686</v>
       </c>
       <c r="N184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2531509995127.8306</v>
       </c>
       <c r="O184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2542601577645.4072</v>
       </c>
       <c r="P184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2553741756930.5186</v>
       </c>
       <c r="Q184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2564930745905.5142</v>
       </c>
       <c r="R184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2576168758425.644</v>
       </c>
       <c r="S184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2587456009283.146</v>
       </c>
       <c r="T184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2598792714211.3501</v>
       </c>
       <c r="U184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2610179089888.8032</v>
       </c>
       <c r="V184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2621615353943.4087</v>
       </c>
       <c r="W184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2633101724956.5879</v>
       </c>
       <c r="X184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2644638422467.4565</v>
       </c>
       <c r="Y184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2656225666977.021</v>
       </c>
       <c r="Z184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2667863679952.3926</v>
       </c>
       <c r="AA184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2679552683831.022</v>
       </c>
       <c r="AB184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2691292902024.9482</v>
       </c>
       <c r="AC184" s="27">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>2703084558925.0708</v>
       </c>
     </row>
@@ -52875,111 +52884,111 @@
         <v>29</v>
       </c>
       <c r="C185" s="27">
-        <f>$C43*(1+C95)</f>
+        <f t="shared" si="44"/>
         <v>245035000000</v>
       </c>
       <c r="D185" s="27">
-        <f t="shared" ref="D185:AC185" si="82">C185*(1+D95)</f>
+        <f t="shared" ref="D185:AC185" si="83">C185*(1+D95)</f>
         <v>246036661460.52979</v>
       </c>
       <c r="E185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>247042417542.9769</v>
       </c>
       <c r="F185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>248052284985.46024</v>
       </c>
       <c r="G185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>249066280594.52133</v>
       </c>
       <c r="H185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>250084421245.40399</v>
       </c>
       <c r="I185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>251106723882.33511</v>
       </c>
       <c r="J185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>252133205518.80676</v>
       </c>
       <c r="K185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>253163883237.85925</v>
       </c>
       <c r="L185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>254198774192.36545</v>
       </c>
       <c r="M185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>255237895605.31628</v>
       </c>
       <c r="N185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>256281264770.1073</v>
       </c>
       <c r="O185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>257328899050.82657</v>
       </c>
       <c r="P185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>258380815882.54355</v>
       </c>
       <c r="Q185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>259437032771.59933</v>
       </c>
       <c r="R185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>260497567295.89795</v>
       </c>
       <c r="S185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>261562437105.19891</v>
       </c>
       <c r="T185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>262631659921.41098</v>
       </c>
       <c r="U185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>263705253538.88702</v>
       </c>
       <c r="V185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>264783235824.72021</v>
       </c>
       <c r="W185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>265865624719.04141</v>
       </c>
       <c r="X185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>266952438235.31763</v>
       </c>
       <c r="Y185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>268043694460.65186</v>
       </c>
       <c r="Z185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>269139411556.08417</v>
       </c>
       <c r="AA185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>270239607756.89383</v>
       </c>
       <c r="AB185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>271344301372.90283</v>
       </c>
       <c r="AC185" s="27">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>272453510788.78064</v>
       </c>
     </row>
@@ -52988,111 +52997,111 @@
         <v>30</v>
       </c>
       <c r="C186" s="27">
-        <f>$C44*(1+C96)</f>
+        <f t="shared" si="44"/>
         <v>1617080000000</v>
       </c>
       <c r="D186" s="27">
-        <f t="shared" ref="D186:AC186" si="83">C186*(1+D96)</f>
+        <f t="shared" ref="D186:AC186" si="84">C186*(1+D96)</f>
         <v>1655830764310.885</v>
       </c>
       <c r="E186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1695510129392.7136</v>
       </c>
       <c r="F186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1736140347694.1057</v>
       </c>
       <c r="G186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1777744204908.4131</v>
       </c>
       <c r="H186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1820345032752.0864</v>
       </c>
       <c r="I186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1863966722049.2554</v>
       </c>
       <c r="J186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1908633736129.8596</v>
       </c>
       <c r="K186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1954371124548.8445</v>
       </c>
       <c r="L186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2001204537134.1162</v>
       </c>
       <c r="M186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2049160238371.1345</v>
       </c>
       <c r="N186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2098265122132.208</v>
       </c>
       <c r="O186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2148546726758.7542</v>
       </c>
       <c r="P186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2200033250504.9829</v>
       </c>
       <c r="Q186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2252753567351.6626</v>
       </c>
       <c r="R186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2306737243198.8374</v>
       </c>
       <c r="S186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2362014552446.5791</v>
       </c>
       <c r="T186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2418616494973.0698</v>
       </c>
       <c r="U186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2476574813519.5361</v>
       </c>
       <c r="V186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2535922011491.7881</v>
       </c>
       <c r="W186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2596691371188.3418</v>
       </c>
       <c r="X186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2658916972465.3521</v>
       </c>
       <c r="Y186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2722633711848.8188</v>
       </c>
       <c r="Z186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2787877322104.7886</v>
       </c>
       <c r="AA186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2854684392278.5239</v>
       </c>
       <c r="AB186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2923092388213.8809</v>
       </c>
       <c r="AC186" s="27">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>2993139673564.4004</v>
       </c>
     </row>
@@ -53101,111 +53110,111 @@
         <v>31</v>
       </c>
       <c r="C187" s="27">
-        <f>$C45*(1+C97)</f>
+        <f t="shared" si="44"/>
         <v>567715000000</v>
       </c>
       <c r="D187" s="27">
-        <f t="shared" ref="D187:AC187" si="84">C187*(1+D97)</f>
+        <f t="shared" ref="D187:AC187" si="85">C187*(1+D97)</f>
         <v>578260898834.31165</v>
       </c>
       <c r="E187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>589002698749.66492</v>
       </c>
       <c r="F187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>599944038813.16602</v>
       </c>
       <c r="G187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>611088625691.39185</v>
       </c>
       <c r="H187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>622440234906.12097</v>
       </c>
       <c r="I187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>634002712113.39075</v>
       </c>
       <c r="J187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>645779974406.31421</v>
       </c>
       <c r="K187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>657776011642.09863</v>
       </c>
       <c r="L187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>669994887793.71448</v>
       </c>
       <c r="M187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>682440742326.67297</v>
       </c>
       <c r="N187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>695117791601.37891</v>
       </c>
       <c r="O187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>708030330301.53357</v>
       </c>
       <c r="P187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>721182732889.07178</v>
       </c>
       <c r="Q187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>734579455086.12585</v>
       </c>
       <c r="R187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>748225035384.51868</v>
       </c>
       <c r="S187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>762124096583.29688</v>
       </c>
       <c r="T187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>776281347354.82593</v>
       </c>
       <c r="U187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>790701583839.97632</v>
       </c>
       <c r="V187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>805389691272.9425</v>
       </c>
       <c r="W187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>820350645636.24438</v>
       </c>
       <c r="X187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>835589515346.47241</v>
       </c>
       <c r="Y187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>851111462971.34656</v>
       </c>
       <c r="Z187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>866921746978.67212</v>
       </c>
       <c r="AA187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>883025723517.78381</v>
       </c>
       <c r="AB187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>899428848234.08228</v>
       </c>
       <c r="AC187" s="27">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>916136678117.27734</v>
       </c>
     </row>
@@ -53214,111 +53223,111 @@
         <v>32</v>
       </c>
       <c r="C188" s="27">
-        <f>$C46*(1+C98)</f>
+        <f t="shared" si="44"/>
         <v>11489000000</v>
       </c>
       <c r="D188" s="27">
-        <f t="shared" ref="D188:AC188" si="85">C188*(1+D98)</f>
+        <f t="shared" ref="D188:AC188" si="86">C188*(1+D98)</f>
         <v>11667883730.000002</v>
       </c>
       <c r="E188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>11849552679.676104</v>
       </c>
       <c r="F188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12034050214.898661</v>
       </c>
       <c r="G188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12221420376.744635</v>
       </c>
       <c r="H188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12411707892.01055</v>
       </c>
       <c r="I188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12604958183.889154</v>
       </c>
       <c r="J188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12801217382.812309</v>
       </c>
       <c r="K188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>13000532337.462698</v>
       </c>
       <c r="L188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>13202950625.956993</v>
       </c>
       <c r="M188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>13408520567.203144</v>
       </c>
       <c r="N188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>13617291232.434498</v>
       </c>
       <c r="O188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>13829312456.923504</v>
       </c>
       <c r="P188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>14044634851.877804</v>
       </c>
       <c r="Q188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>14263309816.521542</v>
       </c>
       <c r="R188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>14485389550.364782</v>
       </c>
       <c r="S188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>14710927065.663963</v>
       </c>
       <c r="T188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>14939976200.076353</v>
       </c>
       <c r="U188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>15172591629.511543</v>
       </c>
       <c r="V188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>15408828881.183039</v>
       </c>
       <c r="W188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>15648744346.86306</v>
       </c>
       <c r="X188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>15892395296.343719</v>
       </c>
       <c r="Y188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>16139839891.107792</v>
       </c>
       <c r="Z188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>16391137198.212341</v>
       </c>
       <c r="AA188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>16646347204.38851</v>
       </c>
       <c r="AB188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>16905530830.36084</v>
       </c>
       <c r="AC188" s="27">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>17168749945.389559</v>
       </c>
     </row>
